--- a/output/notebooks/resumen_tratamientos_seguridad.xlsx
+++ b/output/notebooks/resumen_tratamientos_seguridad.xlsx
@@ -485,16 +485,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C3" t="n">
-        <v>35.89</v>
+        <v>37.5</v>
       </c>
       <c r="D3" t="n">
         <v>37.5</v>
       </c>
       <c r="E3" t="n">
-        <v>12.88</v>
+        <v>11.86</v>
       </c>
       <c r="F3" t="n">
         <v>10</v>
@@ -585,16 +585,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C7" t="n">
-        <v>39.92</v>
+        <v>40.73</v>
       </c>
       <c r="D7" t="n">
-        <v>41.25</v>
+        <v>42.5</v>
       </c>
       <c r="E7" t="n">
-        <v>14.18</v>
+        <v>13.65</v>
       </c>
       <c r="F7" t="n">
         <v>10</v>
